--- a/data/trans_orig/P6902-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6902-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35999</t>
+          <t>35254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>34673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45673</t>
+          <t>46068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>49950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75156</t>
+          <t>74930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35326</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54060</t>
+          <t>53431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>90904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122321</t>
+          <t>121623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67135</t>
+          <t>67361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91257</t>
+          <t>92341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99245</t>
+          <t>99943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128745</t>
+          <t>130662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45760</t>
+          <t>47861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68817</t>
+          <t>70299</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43701</t>
+          <t>43470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80159</t>
+          <t>79154</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107394</t>
+          <t>107099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57211</t>
+          <t>55729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80268</t>
+          <t>78167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42877</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88676</t>
+          <t>88971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115911</t>
+          <t>116916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>41177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62215</t>
+          <t>62767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57090</t>
+          <t>57212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82797</t>
+          <t>83033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48895</t>
+          <t>48343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70185</t>
+          <t>69933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65350</t>
+          <t>65114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91057</t>
+          <t>90935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21411</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>25171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37218</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33719</t>
+          <t>33115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48087</t>
+          <t>46996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>821</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,97 +2904,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>182842</t>
+          <t>185412</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>226766</t>
+          <t>229307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99095</t>
+          <t>97668</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129325</t>
+          <t>126680</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>292085</t>
+          <t>292908</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>345489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>245539</t>
+          <t>242998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>289463</t>
+          <t>286893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90796</t>
+          <t>93441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>121026</t>
+          <t>122453</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>348448</t>
+          <t>346938</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>400342</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35773</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>56027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44464</t>
+          <t>44728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>69697</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96511</t>
+          <t>95551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30777</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>49577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22648</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56889</t>
+          <t>57849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83355</t>
+          <t>83703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37208</t>
+          <t>36894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56829</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52320</t>
+          <t>52937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77270</t>
+          <t>76519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105088</t>
+          <t>103621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41047</t>
+          <t>41868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>60982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65419</t>
+          <t>66886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93237</t>
+          <t>93988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43642</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>44094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66843</t>
+          <t>67911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>45776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63724</t>
+          <t>63764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27711</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63383</t>
+          <t>62315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86127</t>
+          <t>86132</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>43245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28713</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14754</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>23171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40106</t>
+          <t>39421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>134651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170842</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108010</t>
+          <t>107731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>138217</t>
+          <t>138490</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>252559</t>
+          <t>251828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>300396</t>
+          <t>299706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154263</t>
+          <t>154734</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191949</t>
+          <t>190454</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77611</t>
+          <t>77338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>108097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>240537</t>
+          <t>241227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>289105</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20426</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34251</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>45901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68432</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43224</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60444</t>
+          <t>59953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59431</t>
+          <t>58997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80697</t>
+          <t>81962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>33279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54616</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35854</t>
+          <t>36475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>52446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75123</t>
+          <t>74247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>101408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>57339</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79830</t>
+          <t>79844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>34983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82686</t>
+          <t>83173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109458</t>
+          <t>110334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36785</t>
+          <t>36312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>55802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>39097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>64764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90194</t>
+          <t>90228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>35626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54643</t>
+          <t>55116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32227</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57341</t>
+          <t>57307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82232</t>
+          <t>82771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31387</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>24951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52810</t>
+          <t>53460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>27102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>41275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -8406,97 +8406,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>1880</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,97 +8519,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132290</t>
+          <t>132941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170699</t>
+          <t>171739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145027</t>
+          <t>144767</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>256966</t>
+          <t>258995</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>307060</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>179302</t>
+          <t>178262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>217711</t>
+          <t>217060</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71271</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>100351</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>259239</t>
+          <t>258428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>309333</t>
+          <t>307304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,44 +9690,44 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>96,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13030</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8286</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15344</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>54,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13030</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8292</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>54,04%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51480</t>
+          <t>52485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>40790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66154</t>
+          <t>67865</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25627</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42868</t>
+          <t>41157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41573</t>
+          <t>41163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61749</t>
+          <t>62219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>52540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84746</t>
+          <t>85067</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110482</t>
+          <t>109347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33782</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>54368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60602</t>
+          <t>61737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86338</t>
+          <t>86017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56394</t>
+          <t>57196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76617</t>
+          <t>77371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40377</t>
+          <t>39447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107101</t>
+          <t>109072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101449</t>
+          <t>94669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177887</t>
+          <t>177022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31936</t>
+          <t>31182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52159</t>
+          <t>51357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>45877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114572</t>
+          <t>115502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>86480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162053</t>
+          <t>168833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>34359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49969</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>31628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>41739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69639</t>
+          <t>70544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88372</t>
+          <t>88059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17467</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53304</t>
+          <t>52399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>361</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>191466</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227618</t>
+          <t>227815</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149821</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>243927</t>
+          <t>241655</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>354902</t>
+          <t>349388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>460070</t>
+          <t>456275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111887</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>148039</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110288</t>
+          <t>112560</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204394</t>
+          <t>202758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>233650</t>
+          <t>237445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>338818</t>
+          <t>344332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
